--- a/uploads_templates/uploads_for_validation/1.headcount_plan.xlsx
+++ b/uploads_templates/uploads_for_validation/1.headcount_plan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude\Moove\RCCP\uploads_templates\uploads_for_validation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9017D5-A29D-4056-BF4A-468F019943B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A75CA581-4817-4F6C-9D0D-758BEBD0BF54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11220" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Data" sheetId="1" r:id="rId1"/>
     <sheet name="Instructions" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$2:$F$851</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -1376,6 +1379,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:F851"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1427,7 +1431,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1463,7 +1467,7 @@
       </c>
       <c r="F4" s="3"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
@@ -1481,7 +1485,7 @@
       </c>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
@@ -1517,7 +1521,7 @@
       </c>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>16</v>
       </c>
@@ -1535,7 +1539,7 @@
       </c>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
@@ -1571,7 +1575,7 @@
       </c>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>16</v>
       </c>
@@ -1589,7 +1593,7 @@
       </c>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
@@ -1625,7 +1629,7 @@
       </c>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1643,7 +1647,7 @@
       </c>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>12</v>
       </c>
@@ -1679,7 +1683,7 @@
       </c>
       <c r="F16" s="3"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
@@ -1697,7 +1701,7 @@
       </c>
       <c r="F17" s="3"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
@@ -1733,7 +1737,7 @@
       </c>
       <c r="F19" s="3"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>16</v>
       </c>
@@ -1751,7 +1755,7 @@
       </c>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>12</v>
       </c>
@@ -1777,7 +1781,7 @@
         <v>22</v>
       </c>
       <c r="C22" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>14</v>
@@ -1787,7 +1791,7 @@
       </c>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>16</v>
       </c>
@@ -1805,7 +1809,7 @@
       </c>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>12</v>
       </c>
@@ -1831,7 +1835,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>14</v>
@@ -1841,7 +1845,7 @@
       </c>
       <c r="F25" s="3"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>16</v>
       </c>
@@ -1859,7 +1863,7 @@
       </c>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>12</v>
       </c>
@@ -1885,7 +1889,7 @@
         <v>24</v>
       </c>
       <c r="C28" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>14</v>
@@ -1895,7 +1899,7 @@
       </c>
       <c r="F28" s="3"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>16</v>
       </c>
@@ -1913,7 +1917,7 @@
       </c>
       <c r="F29" s="3"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>12</v>
       </c>
@@ -1939,7 +1943,7 @@
         <v>25</v>
       </c>
       <c r="C31" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>14</v>
@@ -1949,7 +1953,7 @@
       </c>
       <c r="F31" s="3"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>16</v>
       </c>
@@ -1967,7 +1971,7 @@
       </c>
       <c r="F32" s="3"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>12</v>
       </c>
@@ -1993,7 +1997,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>14</v>
@@ -2003,7 +2007,7 @@
       </c>
       <c r="F34" s="3"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>16</v>
       </c>
@@ -2021,7 +2025,7 @@
       </c>
       <c r="F35" s="3"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>12</v>
       </c>
@@ -2047,7 +2051,7 @@
         <v>27</v>
       </c>
       <c r="C37" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>14</v>
@@ -2057,7 +2061,7 @@
       </c>
       <c r="F37" s="3"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>16</v>
       </c>
@@ -2075,7 +2079,7 @@
       </c>
       <c r="F38" s="3"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>12</v>
       </c>
@@ -2101,7 +2105,7 @@
         <v>28</v>
       </c>
       <c r="C40" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>14</v>
@@ -2111,7 +2115,7 @@
       </c>
       <c r="F40" s="3"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2129,7 +2133,7 @@
       </c>
       <c r="F41" s="3"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>12</v>
       </c>
@@ -2155,7 +2159,7 @@
         <v>29</v>
       </c>
       <c r="C43" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>14</v>
@@ -2165,7 +2169,7 @@
       </c>
       <c r="F43" s="3"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>16</v>
       </c>
@@ -2183,7 +2187,7 @@
       </c>
       <c r="F44" s="3"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>12</v>
       </c>
@@ -2209,7 +2213,7 @@
         <v>30</v>
       </c>
       <c r="C46" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>14</v>
@@ -2219,7 +2223,7 @@
       </c>
       <c r="F46" s="3"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>16</v>
       </c>
@@ -2237,7 +2241,7 @@
       </c>
       <c r="F47" s="3"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>12</v>
       </c>
@@ -2263,7 +2267,7 @@
         <v>31</v>
       </c>
       <c r="C49" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>14</v>
@@ -2273,7 +2277,7 @@
       </c>
       <c r="F49" s="3"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>16</v>
       </c>
@@ -2291,7 +2295,7 @@
       </c>
       <c r="F50" s="3"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>12</v>
       </c>
@@ -2317,7 +2321,7 @@
         <v>32</v>
       </c>
       <c r="C52" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>14</v>
@@ -2327,7 +2331,7 @@
       </c>
       <c r="F52" s="3"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>16</v>
       </c>
@@ -2345,7 +2349,7 @@
       </c>
       <c r="F53" s="3"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>12</v>
       </c>
@@ -2371,7 +2375,7 @@
         <v>33</v>
       </c>
       <c r="C55" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>14</v>
@@ -2381,7 +2385,7 @@
       </c>
       <c r="F55" s="3"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>16</v>
       </c>
@@ -2399,7 +2403,7 @@
       </c>
       <c r="F56" s="3"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>12</v>
       </c>
@@ -2425,7 +2429,7 @@
         <v>34</v>
       </c>
       <c r="C58" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>14</v>
@@ -2435,7 +2439,7 @@
       </c>
       <c r="F58" s="3"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>16</v>
       </c>
@@ -2453,7 +2457,7 @@
       </c>
       <c r="F59" s="3"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>12</v>
       </c>
@@ -2479,7 +2483,7 @@
         <v>35</v>
       </c>
       <c r="C61" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>14</v>
@@ -2489,7 +2493,7 @@
       </c>
       <c r="F61" s="3"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>16</v>
       </c>
@@ -2507,7 +2511,7 @@
       </c>
       <c r="F62" s="3"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>12</v>
       </c>
@@ -2533,7 +2537,7 @@
         <v>36</v>
       </c>
       <c r="C64" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>14</v>
@@ -2543,7 +2547,7 @@
       </c>
       <c r="F64" s="3"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>16</v>
       </c>
@@ -2561,7 +2565,7 @@
       </c>
       <c r="F65" s="3"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>12</v>
       </c>
@@ -2597,7 +2601,7 @@
       </c>
       <c r="F67" s="3"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>16</v>
       </c>
@@ -2615,7 +2619,7 @@
       </c>
       <c r="F68" s="3"/>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>12</v>
       </c>
@@ -2651,7 +2655,7 @@
       </c>
       <c r="F70" s="3"/>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>16</v>
       </c>
@@ -2669,7 +2673,7 @@
       </c>
       <c r="F71" s="3"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>12</v>
       </c>
@@ -2705,7 +2709,7 @@
       </c>
       <c r="F73" s="3"/>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>16</v>
       </c>
@@ -2723,7 +2727,7 @@
       </c>
       <c r="F74" s="3"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>12</v>
       </c>
@@ -2759,7 +2763,7 @@
       </c>
       <c r="F76" s="3"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>16</v>
       </c>
@@ -2777,7 +2781,7 @@
       </c>
       <c r="F77" s="3"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>12</v>
       </c>
@@ -2813,7 +2817,7 @@
       </c>
       <c r="F79" s="3"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>16</v>
       </c>
@@ -2831,7 +2835,7 @@
       </c>
       <c r="F80" s="3"/>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>12</v>
       </c>
@@ -2867,7 +2871,7 @@
       </c>
       <c r="F82" s="3"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>16</v>
       </c>
@@ -2885,7 +2889,7 @@
       </c>
       <c r="F83" s="3"/>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>12</v>
       </c>
@@ -2921,7 +2925,7 @@
       </c>
       <c r="F85" s="3"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>16</v>
       </c>
@@ -2939,7 +2943,7 @@
       </c>
       <c r="F86" s="3"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>12</v>
       </c>
@@ -2975,7 +2979,7 @@
       </c>
       <c r="F88" s="3"/>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>16</v>
       </c>
@@ -2993,7 +2997,7 @@
       </c>
       <c r="F89" s="3"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>12</v>
       </c>
@@ -3029,7 +3033,7 @@
       </c>
       <c r="F91" s="3"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>16</v>
       </c>
@@ -3047,7 +3051,7 @@
       </c>
       <c r="F92" s="3"/>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
         <v>12</v>
       </c>
@@ -3083,7 +3087,7 @@
       </c>
       <c r="F94" s="3"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>16</v>
       </c>
@@ -3101,7 +3105,7 @@
       </c>
       <c r="F95" s="3"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>12</v>
       </c>
@@ -3137,7 +3141,7 @@
       </c>
       <c r="F97" s="3"/>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>16</v>
       </c>
@@ -3155,7 +3159,7 @@
       </c>
       <c r="F98" s="3"/>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>12</v>
       </c>
@@ -3191,7 +3195,7 @@
       </c>
       <c r="F100" s="3"/>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>16</v>
       </c>
@@ -3209,7 +3213,7 @@
       </c>
       <c r="F101" s="3"/>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>12</v>
       </c>
@@ -3245,7 +3249,7 @@
       </c>
       <c r="F103" s="3"/>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
         <v>16</v>
       </c>
@@ -3263,7 +3267,7 @@
       </c>
       <c r="F104" s="3"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
         <v>12</v>
       </c>
@@ -3299,7 +3303,7 @@
       </c>
       <c r="F106" s="3"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
         <v>16</v>
       </c>
@@ -3317,7 +3321,7 @@
       </c>
       <c r="F107" s="3"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>12</v>
       </c>
@@ -3353,7 +3357,7 @@
       </c>
       <c r="F109" s="3"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>16</v>
       </c>
@@ -3371,7 +3375,7 @@
       </c>
       <c r="F110" s="3"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
         <v>12</v>
       </c>
@@ -3407,7 +3411,7 @@
       </c>
       <c r="F112" s="3"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>16</v>
       </c>
@@ -3425,7 +3429,7 @@
       </c>
       <c r="F113" s="3"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>12</v>
       </c>
@@ -3461,7 +3465,7 @@
       </c>
       <c r="F115" s="3"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
         <v>16</v>
       </c>
@@ -3479,7 +3483,7 @@
       </c>
       <c r="F116" s="3"/>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
         <v>12</v>
       </c>
@@ -3515,7 +3519,7 @@
       </c>
       <c r="F118" s="3"/>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>16</v>
       </c>
@@ -3533,7 +3537,7 @@
       </c>
       <c r="F119" s="3"/>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>12</v>
       </c>
@@ -3569,7 +3573,7 @@
       </c>
       <c r="F121" s="3"/>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>16</v>
       </c>
@@ -3587,7 +3591,7 @@
       </c>
       <c r="F122" s="3"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
         <v>12</v>
       </c>
@@ -3623,7 +3627,7 @@
       </c>
       <c r="F124" s="3"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
         <v>16</v>
       </c>
@@ -3641,7 +3645,7 @@
       </c>
       <c r="F125" s="3"/>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
         <v>12</v>
       </c>
@@ -3677,7 +3681,7 @@
       </c>
       <c r="F127" s="3"/>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
         <v>16</v>
       </c>
@@ -3695,7 +3699,7 @@
       </c>
       <c r="F128" s="3"/>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
         <v>12</v>
       </c>
@@ -3731,7 +3735,7 @@
       </c>
       <c r="F130" s="3"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
         <v>16</v>
       </c>
@@ -3749,7 +3753,7 @@
       </c>
       <c r="F131" s="3"/>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>12</v>
       </c>
@@ -3785,7 +3789,7 @@
       </c>
       <c r="F133" s="3"/>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
         <v>16</v>
       </c>
@@ -3803,7 +3807,7 @@
       </c>
       <c r="F134" s="3"/>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>12</v>
       </c>
@@ -3839,7 +3843,7 @@
       </c>
       <c r="F136" s="3"/>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
         <v>16</v>
       </c>
@@ -3857,7 +3861,7 @@
       </c>
       <c r="F137" s="3"/>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>12</v>
       </c>
@@ -3893,7 +3897,7 @@
       </c>
       <c r="F139" s="3"/>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
         <v>16</v>
       </c>
@@ -3911,7 +3915,7 @@
       </c>
       <c r="F140" s="3"/>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
         <v>12</v>
       </c>
@@ -3947,7 +3951,7 @@
       </c>
       <c r="F142" s="3"/>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
         <v>16</v>
       </c>
@@ -3965,7 +3969,7 @@
       </c>
       <c r="F143" s="3"/>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
         <v>12</v>
       </c>
@@ -4001,7 +4005,7 @@
       </c>
       <c r="F145" s="3"/>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
         <v>16</v>
       </c>
@@ -4019,7 +4023,7 @@
       </c>
       <c r="F146" s="3"/>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
         <v>12</v>
       </c>
@@ -4055,7 +4059,7 @@
       </c>
       <c r="F148" s="3"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
         <v>16</v>
       </c>
@@ -4073,7 +4077,7 @@
       </c>
       <c r="F149" s="3"/>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
         <v>12</v>
       </c>
@@ -4109,7 +4113,7 @@
       </c>
       <c r="F151" s="3"/>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
         <v>16</v>
       </c>
@@ -4127,7 +4131,7 @@
       </c>
       <c r="F152" s="3"/>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
         <v>12</v>
       </c>
@@ -4163,7 +4167,7 @@
       </c>
       <c r="F154" s="3"/>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
         <v>16</v>
       </c>
@@ -4181,7 +4185,7 @@
       </c>
       <c r="F155" s="3"/>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
         <v>12</v>
       </c>
@@ -4217,7 +4221,7 @@
       </c>
       <c r="F157" s="3"/>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
         <v>16</v>
       </c>
@@ -4235,7 +4239,7 @@
       </c>
       <c r="F158" s="3"/>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
         <v>12</v>
       </c>
@@ -4271,7 +4275,7 @@
       </c>
       <c r="F160" s="3"/>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
         <v>16</v>
       </c>
@@ -4289,7 +4293,7 @@
       </c>
       <c r="F161" s="3"/>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
         <v>12</v>
       </c>
@@ -4325,7 +4329,7 @@
       </c>
       <c r="F163" s="3"/>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
         <v>16</v>
       </c>
@@ -4343,7 +4347,7 @@
       </c>
       <c r="F164" s="3"/>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
         <v>12</v>
       </c>
@@ -4379,7 +4383,7 @@
       </c>
       <c r="F166" s="3"/>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
         <v>16</v>
       </c>
@@ -4397,7 +4401,7 @@
       </c>
       <c r="F167" s="3"/>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
         <v>12</v>
       </c>
@@ -4433,7 +4437,7 @@
       </c>
       <c r="F169" s="3"/>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
         <v>16</v>
       </c>
@@ -4451,7 +4455,7 @@
       </c>
       <c r="F170" s="3"/>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
         <v>12</v>
       </c>
@@ -4487,7 +4491,7 @@
       </c>
       <c r="F172" s="3"/>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
         <v>16</v>
       </c>
@@ -4505,7 +4509,7 @@
       </c>
       <c r="F173" s="3"/>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
         <v>12</v>
       </c>
@@ -4541,7 +4545,7 @@
       </c>
       <c r="F175" s="3"/>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
         <v>16</v>
       </c>
@@ -4559,7 +4563,7 @@
       </c>
       <c r="F176" s="3"/>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
         <v>12</v>
       </c>
@@ -4595,7 +4599,7 @@
       </c>
       <c r="F178" s="3"/>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
         <v>16</v>
       </c>
@@ -4613,7 +4617,7 @@
       </c>
       <c r="F179" s="3"/>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
         <v>12</v>
       </c>
@@ -4649,7 +4653,7 @@
       </c>
       <c r="F181" s="3"/>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
         <v>16</v>
       </c>
@@ -4667,7 +4671,7 @@
       </c>
       <c r="F182" s="3"/>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
         <v>12</v>
       </c>
@@ -4703,7 +4707,7 @@
       </c>
       <c r="F184" s="3"/>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
         <v>16</v>
       </c>
@@ -4721,7 +4725,7 @@
       </c>
       <c r="F185" s="3"/>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
         <v>12</v>
       </c>
@@ -4757,7 +4761,7 @@
       </c>
       <c r="F187" s="3"/>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
         <v>16</v>
       </c>
@@ -4775,7 +4779,7 @@
       </c>
       <c r="F188" s="3"/>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
         <v>12</v>
       </c>
@@ -4811,7 +4815,7 @@
       </c>
       <c r="F190" s="3"/>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
         <v>16</v>
       </c>
@@ -4829,7 +4833,7 @@
       </c>
       <c r="F191" s="3"/>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
         <v>12</v>
       </c>
@@ -4865,7 +4869,7 @@
       </c>
       <c r="F193" s="3"/>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
         <v>16</v>
       </c>
@@ -4883,7 +4887,7 @@
       </c>
       <c r="F194" s="3"/>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
         <v>12</v>
       </c>
@@ -4919,7 +4923,7 @@
       </c>
       <c r="F196" s="3"/>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
         <v>16</v>
       </c>
@@ -4937,7 +4941,7 @@
       </c>
       <c r="F197" s="3"/>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
         <v>12</v>
       </c>
@@ -4973,7 +4977,7 @@
       </c>
       <c r="F199" s="3"/>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
         <v>16</v>
       </c>
@@ -4991,7 +4995,7 @@
       </c>
       <c r="F200" s="3"/>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
         <v>12</v>
       </c>
@@ -5027,7 +5031,7 @@
       </c>
       <c r="F202" s="3"/>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
         <v>16</v>
       </c>
@@ -5045,7 +5049,7 @@
       </c>
       <c r="F203" s="3"/>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
         <v>12</v>
       </c>
@@ -5081,7 +5085,7 @@
       </c>
       <c r="F205" s="3"/>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
         <v>16</v>
       </c>
@@ -5099,7 +5103,7 @@
       </c>
       <c r="F206" s="3"/>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
         <v>12</v>
       </c>
@@ -5135,7 +5139,7 @@
       </c>
       <c r="F208" s="3"/>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
         <v>16</v>
       </c>
@@ -5153,7 +5157,7 @@
       </c>
       <c r="F209" s="3"/>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
         <v>12</v>
       </c>
@@ -5189,7 +5193,7 @@
       </c>
       <c r="F211" s="3"/>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
         <v>16</v>
       </c>
@@ -5207,7 +5211,7 @@
       </c>
       <c r="F212" s="3"/>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
         <v>12</v>
       </c>
@@ -5243,7 +5247,7 @@
       </c>
       <c r="F214" s="3"/>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
         <v>16</v>
       </c>
@@ -5261,7 +5265,7 @@
       </c>
       <c r="F215" s="3"/>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
         <v>12</v>
       </c>
@@ -5297,7 +5301,7 @@
       </c>
       <c r="F217" s="3"/>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="3" t="s">
         <v>16</v>
       </c>
@@ -5315,7 +5319,7 @@
       </c>
       <c r="F218" s="3"/>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
         <v>12</v>
       </c>
@@ -5351,7 +5355,7 @@
       </c>
       <c r="F220" s="3"/>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
         <v>16</v>
       </c>
@@ -5369,7 +5373,7 @@
       </c>
       <c r="F221" s="3"/>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
         <v>12</v>
       </c>
@@ -5405,7 +5409,7 @@
       </c>
       <c r="F223" s="3"/>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
         <v>16</v>
       </c>
@@ -5423,7 +5427,7 @@
       </c>
       <c r="F224" s="3"/>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="3" t="s">
         <v>12</v>
       </c>
@@ -5459,7 +5463,7 @@
       </c>
       <c r="F226" s="3"/>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="3" t="s">
         <v>16</v>
       </c>
@@ -5477,7 +5481,7 @@
       </c>
       <c r="F227" s="3"/>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
         <v>12</v>
       </c>
@@ -5513,7 +5517,7 @@
       </c>
       <c r="F229" s="3"/>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
         <v>16</v>
       </c>
@@ -5531,7 +5535,7 @@
       </c>
       <c r="F230" s="3"/>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
         <v>12</v>
       </c>
@@ -5567,7 +5571,7 @@
       </c>
       <c r="F232" s="3"/>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="3" t="s">
         <v>16</v>
       </c>
@@ -5585,7 +5589,7 @@
       </c>
       <c r="F233" s="3"/>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
         <v>12</v>
       </c>
@@ -5621,7 +5625,7 @@
       </c>
       <c r="F235" s="3"/>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
         <v>16</v>
       </c>
@@ -5639,7 +5643,7 @@
       </c>
       <c r="F236" s="3"/>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
         <v>12</v>
       </c>
@@ -5675,7 +5679,7 @@
       </c>
       <c r="F238" s="3"/>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="3" t="s">
         <v>16</v>
       </c>
@@ -5693,7 +5697,7 @@
       </c>
       <c r="F239" s="3"/>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
         <v>12</v>
       </c>
@@ -5729,7 +5733,7 @@
       </c>
       <c r="F241" s="3"/>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="3" t="s">
         <v>16</v>
       </c>
@@ -5747,7 +5751,7 @@
       </c>
       <c r="F242" s="3"/>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="3" t="s">
         <v>12</v>
       </c>
@@ -5783,7 +5787,7 @@
       </c>
       <c r="F244" s="3"/>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
         <v>16</v>
       </c>
@@ -5801,7 +5805,7 @@
       </c>
       <c r="F245" s="3"/>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
         <v>12</v>
       </c>
@@ -5837,7 +5841,7 @@
       </c>
       <c r="F247" s="3"/>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="3" t="s">
         <v>16</v>
       </c>
@@ -5855,7 +5859,7 @@
       </c>
       <c r="F248" s="3"/>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="3" t="s">
         <v>12</v>
       </c>
@@ -5891,7 +5895,7 @@
       </c>
       <c r="F250" s="3"/>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="3" t="s">
         <v>16</v>
       </c>
@@ -5909,7 +5913,7 @@
       </c>
       <c r="F251" s="3"/>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="3" t="s">
         <v>12</v>
       </c>
@@ -5945,7 +5949,7 @@
       </c>
       <c r="F253" s="3"/>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="3" t="s">
         <v>16</v>
       </c>
@@ -5963,7 +5967,7 @@
       </c>
       <c r="F254" s="3"/>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="3" t="s">
         <v>12</v>
       </c>
@@ -5999,7 +6003,7 @@
       </c>
       <c r="F256" s="3"/>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
         <v>16</v>
       </c>
@@ -6017,7 +6021,7 @@
       </c>
       <c r="F257" s="3"/>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="3" t="s">
         <v>12</v>
       </c>
@@ -6053,7 +6057,7 @@
       </c>
       <c r="F259" s="3"/>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="3" t="s">
         <v>16</v>
       </c>
@@ -6071,7 +6075,7 @@
       </c>
       <c r="F260" s="3"/>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="3" t="s">
         <v>12</v>
       </c>
@@ -6107,7 +6111,7 @@
       </c>
       <c r="F262" s="3"/>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="3" t="s">
         <v>16</v>
       </c>
@@ -6125,7 +6129,7 @@
       </c>
       <c r="F263" s="3"/>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="3" t="s">
         <v>12</v>
       </c>
@@ -6161,7 +6165,7 @@
       </c>
       <c r="F265" s="3"/>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="3" t="s">
         <v>16</v>
       </c>
@@ -6179,7 +6183,7 @@
       </c>
       <c r="F266" s="3"/>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="3" t="s">
         <v>12</v>
       </c>
@@ -6215,7 +6219,7 @@
       </c>
       <c r="F268" s="3"/>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="3" t="s">
         <v>16</v>
       </c>
@@ -6233,7 +6237,7 @@
       </c>
       <c r="F269" s="3"/>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="3" t="s">
         <v>12</v>
       </c>
@@ -6269,7 +6273,7 @@
       </c>
       <c r="F271" s="3"/>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="3" t="s">
         <v>16</v>
       </c>
@@ -6287,7 +6291,7 @@
       </c>
       <c r="F272" s="3"/>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="3" t="s">
         <v>12</v>
       </c>
@@ -6323,7 +6327,7 @@
       </c>
       <c r="F274" s="3"/>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="3" t="s">
         <v>16</v>
       </c>
@@ -6341,7 +6345,7 @@
       </c>
       <c r="F275" s="3"/>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="3" t="s">
         <v>12</v>
       </c>
@@ -6377,7 +6381,7 @@
       </c>
       <c r="F277" s="3"/>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="3" t="s">
         <v>16</v>
       </c>
@@ -6395,7 +6399,7 @@
       </c>
       <c r="F278" s="3"/>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="3" t="s">
         <v>12</v>
       </c>
@@ -6431,7 +6435,7 @@
       </c>
       <c r="F280" s="3"/>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="3" t="s">
         <v>16</v>
       </c>
@@ -6449,7 +6453,7 @@
       </c>
       <c r="F281" s="3"/>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="3" t="s">
         <v>12</v>
       </c>
@@ -6485,7 +6489,7 @@
       </c>
       <c r="F283" s="3"/>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="3" t="s">
         <v>16</v>
       </c>
@@ -6503,7 +6507,7 @@
       </c>
       <c r="F284" s="3"/>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="3" t="s">
         <v>12</v>
       </c>
@@ -6539,7 +6543,7 @@
       </c>
       <c r="F286" s="3"/>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="3" t="s">
         <v>16</v>
       </c>
@@ -6557,7 +6561,7 @@
       </c>
       <c r="F287" s="3"/>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="3" t="s">
         <v>12</v>
       </c>
@@ -6593,7 +6597,7 @@
       </c>
       <c r="F289" s="3"/>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="3" t="s">
         <v>16</v>
       </c>
@@ -6611,7 +6615,7 @@
       </c>
       <c r="F290" s="3"/>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="3" t="s">
         <v>12</v>
       </c>
@@ -6647,7 +6651,7 @@
       </c>
       <c r="F292" s="3"/>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="3" t="s">
         <v>16</v>
       </c>
@@ -6665,7 +6669,7 @@
       </c>
       <c r="F293" s="3"/>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="3" t="s">
         <v>12</v>
       </c>
@@ -6701,7 +6705,7 @@
       </c>
       <c r="F295" s="3"/>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="3" t="s">
         <v>16</v>
       </c>
@@ -6719,7 +6723,7 @@
       </c>
       <c r="F296" s="3"/>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="3" t="s">
         <v>12</v>
       </c>
@@ -6755,7 +6759,7 @@
       </c>
       <c r="F298" s="3"/>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="3" t="s">
         <v>16</v>
       </c>
@@ -6773,7 +6777,7 @@
       </c>
       <c r="F299" s="3"/>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="3" t="s">
         <v>12</v>
       </c>
@@ -6809,7 +6813,7 @@
       </c>
       <c r="F301" s="3"/>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="3" t="s">
         <v>16</v>
       </c>
@@ -6827,7 +6831,7 @@
       </c>
       <c r="F302" s="3"/>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="3" t="s">
         <v>12</v>
       </c>
@@ -6863,7 +6867,7 @@
       </c>
       <c r="F304" s="3"/>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="3" t="s">
         <v>16</v>
       </c>
@@ -6881,7 +6885,7 @@
       </c>
       <c r="F305" s="3"/>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="3" t="s">
         <v>12</v>
       </c>
@@ -6917,7 +6921,7 @@
       </c>
       <c r="F307" s="3"/>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="3" t="s">
         <v>16</v>
       </c>
@@ -6935,7 +6939,7 @@
       </c>
       <c r="F308" s="3"/>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="3" t="s">
         <v>12</v>
       </c>
@@ -6971,7 +6975,7 @@
       </c>
       <c r="F310" s="3"/>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="3" t="s">
         <v>16</v>
       </c>
@@ -6989,7 +6993,7 @@
       </c>
       <c r="F311" s="3"/>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="3" t="s">
         <v>12</v>
       </c>
@@ -7025,7 +7029,7 @@
       </c>
       <c r="F313" s="3"/>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="3" t="s">
         <v>16</v>
       </c>
@@ -7043,7 +7047,7 @@
       </c>
       <c r="F314" s="3"/>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="3" t="s">
         <v>12</v>
       </c>
@@ -7079,7 +7083,7 @@
       </c>
       <c r="F316" s="3"/>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="3" t="s">
         <v>16</v>
       </c>
@@ -7097,7 +7101,7 @@
       </c>
       <c r="F317" s="3"/>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="3" t="s">
         <v>12</v>
       </c>
@@ -7133,7 +7137,7 @@
       </c>
       <c r="F319" s="3"/>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="3" t="s">
         <v>16</v>
       </c>
@@ -7151,7 +7155,7 @@
       </c>
       <c r="F320" s="3"/>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="3" t="s">
         <v>12</v>
       </c>
@@ -7187,7 +7191,7 @@
       </c>
       <c r="F322" s="3"/>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="3" t="s">
         <v>16</v>
       </c>
@@ -7205,7 +7209,7 @@
       </c>
       <c r="F323" s="3"/>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="3" t="s">
         <v>12</v>
       </c>
@@ -7241,7 +7245,7 @@
       </c>
       <c r="F325" s="3"/>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="3" t="s">
         <v>16</v>
       </c>
@@ -7259,7 +7263,7 @@
       </c>
       <c r="F326" s="3"/>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="3" t="s">
         <v>12</v>
       </c>
@@ -7295,7 +7299,7 @@
       </c>
       <c r="F328" s="3"/>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="3" t="s">
         <v>16</v>
       </c>
@@ -7313,7 +7317,7 @@
       </c>
       <c r="F329" s="3"/>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="3" t="s">
         <v>12</v>
       </c>
@@ -7349,7 +7353,7 @@
       </c>
       <c r="F331" s="3"/>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="3" t="s">
         <v>16</v>
       </c>
@@ -7367,7 +7371,7 @@
       </c>
       <c r="F332" s="3"/>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="3" t="s">
         <v>12</v>
       </c>
@@ -7403,7 +7407,7 @@
       </c>
       <c r="F334" s="3"/>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="3" t="s">
         <v>16</v>
       </c>
@@ -7421,7 +7425,7 @@
       </c>
       <c r="F335" s="3"/>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="3" t="s">
         <v>12</v>
       </c>
@@ -7457,7 +7461,7 @@
       </c>
       <c r="F337" s="3"/>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="3" t="s">
         <v>16</v>
       </c>
@@ -7475,7 +7479,7 @@
       </c>
       <c r="F338" s="3"/>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="3" t="s">
         <v>12</v>
       </c>
@@ -7511,7 +7515,7 @@
       </c>
       <c r="F340" s="3"/>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="3" t="s">
         <v>16</v>
       </c>
@@ -7529,7 +7533,7 @@
       </c>
       <c r="F341" s="3"/>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="3" t="s">
         <v>12</v>
       </c>
@@ -7565,7 +7569,7 @@
       </c>
       <c r="F343" s="3"/>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="3" t="s">
         <v>16</v>
       </c>
@@ -7583,7 +7587,7 @@
       </c>
       <c r="F344" s="3"/>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="3" t="s">
         <v>12</v>
       </c>
@@ -7619,7 +7623,7 @@
       </c>
       <c r="F346" s="3"/>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="3" t="s">
         <v>16</v>
       </c>
@@ -7637,7 +7641,7 @@
       </c>
       <c r="F347" s="3"/>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="3" t="s">
         <v>12</v>
       </c>
@@ -7673,7 +7677,7 @@
       </c>
       <c r="F349" s="3"/>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="3" t="s">
         <v>16</v>
       </c>
@@ -7691,7 +7695,7 @@
       </c>
       <c r="F350" s="3"/>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="3" t="s">
         <v>12</v>
       </c>
@@ -7727,7 +7731,7 @@
       </c>
       <c r="F352" s="3"/>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="3" t="s">
         <v>16</v>
       </c>
@@ -7745,7 +7749,7 @@
       </c>
       <c r="F353" s="3"/>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="3" t="s">
         <v>12</v>
       </c>
@@ -7781,7 +7785,7 @@
       </c>
       <c r="F355" s="3"/>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="3" t="s">
         <v>16</v>
       </c>
@@ -7799,7 +7803,7 @@
       </c>
       <c r="F356" s="3"/>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="3" t="s">
         <v>12</v>
       </c>
@@ -7835,7 +7839,7 @@
       </c>
       <c r="F358" s="3"/>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="3" t="s">
         <v>16</v>
       </c>
@@ -7853,7 +7857,7 @@
       </c>
       <c r="F359" s="3"/>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="3" t="s">
         <v>12</v>
       </c>
@@ -7889,7 +7893,7 @@
       </c>
       <c r="F361" s="3"/>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="3" t="s">
         <v>16</v>
       </c>
@@ -7907,7 +7911,7 @@
       </c>
       <c r="F362" s="3"/>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="3" t="s">
         <v>12</v>
       </c>
@@ -7943,7 +7947,7 @@
       </c>
       <c r="F364" s="3"/>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="3" t="s">
         <v>16</v>
       </c>
@@ -7961,7 +7965,7 @@
       </c>
       <c r="F365" s="3"/>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="3" t="s">
         <v>12</v>
       </c>
@@ -7997,7 +8001,7 @@
       </c>
       <c r="F367" s="3"/>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="3" t="s">
         <v>16</v>
       </c>
@@ -8015,7 +8019,7 @@
       </c>
       <c r="F368" s="3"/>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="3" t="s">
         <v>12</v>
       </c>
@@ -8051,7 +8055,7 @@
       </c>
       <c r="F370" s="3"/>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="3" t="s">
         <v>16</v>
       </c>
@@ -8069,7 +8073,7 @@
       </c>
       <c r="F371" s="3"/>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="3" t="s">
         <v>12</v>
       </c>
@@ -8105,7 +8109,7 @@
       </c>
       <c r="F373" s="3"/>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="3" t="s">
         <v>16</v>
       </c>
@@ -8123,7 +8127,7 @@
       </c>
       <c r="F374" s="3"/>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="3" t="s">
         <v>12</v>
       </c>
@@ -8159,7 +8163,7 @@
       </c>
       <c r="F376" s="3"/>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="3" t="s">
         <v>16</v>
       </c>
@@ -8177,7 +8181,7 @@
       </c>
       <c r="F377" s="3"/>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="3" t="s">
         <v>12</v>
       </c>
@@ -8213,7 +8217,7 @@
       </c>
       <c r="F379" s="3"/>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="3" t="s">
         <v>16</v>
       </c>
@@ -8231,7 +8235,7 @@
       </c>
       <c r="F380" s="3"/>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="3" t="s">
         <v>12</v>
       </c>
@@ -8267,7 +8271,7 @@
       </c>
       <c r="F382" s="3"/>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="3" t="s">
         <v>16</v>
       </c>
@@ -8285,7 +8289,7 @@
       </c>
       <c r="F383" s="3"/>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="3" t="s">
         <v>12</v>
       </c>
@@ -8321,7 +8325,7 @@
       </c>
       <c r="F385" s="3"/>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="3" t="s">
         <v>16</v>
       </c>
@@ -8339,7 +8343,7 @@
       </c>
       <c r="F386" s="3"/>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="3" t="s">
         <v>12</v>
       </c>
@@ -8375,7 +8379,7 @@
       </c>
       <c r="F388" s="3"/>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="3" t="s">
         <v>16</v>
       </c>
@@ -8393,7 +8397,7 @@
       </c>
       <c r="F389" s="3"/>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="3" t="s">
         <v>12</v>
       </c>
@@ -8429,7 +8433,7 @@
       </c>
       <c r="F391" s="3"/>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="3" t="s">
         <v>16</v>
       </c>
@@ -8447,7 +8451,7 @@
       </c>
       <c r="F392" s="3"/>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="3" t="s">
         <v>12</v>
       </c>
@@ -8483,7 +8487,7 @@
       </c>
       <c r="F394" s="3"/>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="3" t="s">
         <v>16</v>
       </c>
@@ -8501,7 +8505,7 @@
       </c>
       <c r="F395" s="3"/>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="3" t="s">
         <v>12</v>
       </c>
@@ -8537,7 +8541,7 @@
       </c>
       <c r="F397" s="3"/>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="3" t="s">
         <v>16</v>
       </c>
@@ -8555,7 +8559,7 @@
       </c>
       <c r="F398" s="3"/>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="3" t="s">
         <v>12</v>
       </c>
@@ -8591,7 +8595,7 @@
       </c>
       <c r="F400" s="3"/>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="3" t="s">
         <v>16</v>
       </c>
@@ -8609,7 +8613,7 @@
       </c>
       <c r="F401" s="3"/>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="3" t="s">
         <v>12</v>
       </c>
@@ -8645,7 +8649,7 @@
       </c>
       <c r="F403" s="3"/>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="3" t="s">
         <v>16</v>
       </c>
@@ -8663,7 +8667,7 @@
       </c>
       <c r="F404" s="3"/>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="3" t="s">
         <v>12</v>
       </c>
@@ -8699,7 +8703,7 @@
       </c>
       <c r="F406" s="3"/>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="3" t="s">
         <v>16</v>
       </c>
@@ -8717,7 +8721,7 @@
       </c>
       <c r="F407" s="3"/>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="3" t="s">
         <v>12</v>
       </c>
@@ -8753,7 +8757,7 @@
       </c>
       <c r="F409" s="3"/>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="3" t="s">
         <v>16</v>
       </c>
@@ -8771,7 +8775,7 @@
       </c>
       <c r="F410" s="3"/>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="3" t="s">
         <v>12</v>
       </c>
@@ -8807,7 +8811,7 @@
       </c>
       <c r="F412" s="3"/>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="3" t="s">
         <v>16</v>
       </c>
@@ -8825,7 +8829,7 @@
       </c>
       <c r="F413" s="3"/>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="3" t="s">
         <v>12</v>
       </c>
@@ -8861,7 +8865,7 @@
       </c>
       <c r="F415" s="3"/>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="3" t="s">
         <v>16</v>
       </c>
@@ -8879,7 +8883,7 @@
       </c>
       <c r="F416" s="3"/>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="3" t="s">
         <v>12</v>
       </c>
@@ -8915,7 +8919,7 @@
       </c>
       <c r="F418" s="3"/>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" s="3" t="s">
         <v>16</v>
       </c>
@@ -8933,7 +8937,7 @@
       </c>
       <c r="F419" s="3"/>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" s="3" t="s">
         <v>12</v>
       </c>
@@ -8969,7 +8973,7 @@
       </c>
       <c r="F421" s="3"/>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" s="3" t="s">
         <v>16</v>
       </c>
@@ -8987,7 +8991,7 @@
       </c>
       <c r="F422" s="3"/>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" s="3" t="s">
         <v>12</v>
       </c>
@@ -9023,7 +9027,7 @@
       </c>
       <c r="F424" s="3"/>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" s="3" t="s">
         <v>16</v>
       </c>
@@ -9041,7 +9045,7 @@
       </c>
       <c r="F425" s="3"/>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" s="3" t="s">
         <v>12</v>
       </c>
@@ -9077,7 +9081,7 @@
       </c>
       <c r="F427" s="3"/>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" s="3" t="s">
         <v>16</v>
       </c>
@@ -9095,7 +9099,7 @@
       </c>
       <c r="F428" s="3"/>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" s="3" t="s">
         <v>12</v>
       </c>
@@ -9131,7 +9135,7 @@
       </c>
       <c r="F430" s="3"/>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" s="3" t="s">
         <v>16</v>
       </c>
@@ -9149,7 +9153,7 @@
       </c>
       <c r="F431" s="3"/>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" s="3" t="s">
         <v>12</v>
       </c>
@@ -9185,7 +9189,7 @@
       </c>
       <c r="F433" s="3"/>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" s="3" t="s">
         <v>16</v>
       </c>
@@ -9203,7 +9207,7 @@
       </c>
       <c r="F434" s="3"/>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" s="3" t="s">
         <v>12</v>
       </c>
@@ -9239,7 +9243,7 @@
       </c>
       <c r="F436" s="3"/>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" s="3" t="s">
         <v>16</v>
       </c>
@@ -9257,7 +9261,7 @@
       </c>
       <c r="F437" s="3"/>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" s="3" t="s">
         <v>12</v>
       </c>
@@ -9293,7 +9297,7 @@
       </c>
       <c r="F439" s="3"/>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" s="3" t="s">
         <v>16</v>
       </c>
@@ -9311,7 +9315,7 @@
       </c>
       <c r="F440" s="3"/>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" s="3" t="s">
         <v>12</v>
       </c>
@@ -9347,7 +9351,7 @@
       </c>
       <c r="F442" s="3"/>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" s="3" t="s">
         <v>16</v>
       </c>
@@ -9365,7 +9369,7 @@
       </c>
       <c r="F443" s="3"/>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" s="3" t="s">
         <v>12</v>
       </c>
@@ -9401,7 +9405,7 @@
       </c>
       <c r="F445" s="3"/>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" s="3" t="s">
         <v>16</v>
       </c>
@@ -9419,7 +9423,7 @@
       </c>
       <c r="F446" s="3"/>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" s="3" t="s">
         <v>12</v>
       </c>
@@ -9455,7 +9459,7 @@
       </c>
       <c r="F448" s="3"/>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" s="3" t="s">
         <v>16</v>
       </c>
@@ -9473,7 +9477,7 @@
       </c>
       <c r="F449" s="3"/>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" s="3" t="s">
         <v>12</v>
       </c>
@@ -9509,7 +9513,7 @@
       </c>
       <c r="F451" s="3"/>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" s="3" t="s">
         <v>16</v>
       </c>
@@ -9527,7 +9531,7 @@
       </c>
       <c r="F452" s="3"/>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" s="3" t="s">
         <v>12</v>
       </c>
@@ -9563,7 +9567,7 @@
       </c>
       <c r="F454" s="3"/>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" s="3" t="s">
         <v>16</v>
       </c>
@@ -9581,7 +9585,7 @@
       </c>
       <c r="F455" s="3"/>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" s="3" t="s">
         <v>12</v>
       </c>
@@ -9617,7 +9621,7 @@
       </c>
       <c r="F457" s="3"/>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" s="3" t="s">
         <v>16</v>
       </c>
@@ -9635,7 +9639,7 @@
       </c>
       <c r="F458" s="3"/>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" s="3" t="s">
         <v>12</v>
       </c>
@@ -9671,7 +9675,7 @@
       </c>
       <c r="F460" s="3"/>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" s="3" t="s">
         <v>16</v>
       </c>
@@ -9689,7 +9693,7 @@
       </c>
       <c r="F461" s="3"/>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" s="3" t="s">
         <v>12</v>
       </c>
@@ -9725,7 +9729,7 @@
       </c>
       <c r="F463" s="3"/>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" s="3" t="s">
         <v>16</v>
       </c>
@@ -9743,7 +9747,7 @@
       </c>
       <c r="F464" s="3"/>
     </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" s="3" t="s">
         <v>12</v>
       </c>
@@ -9779,7 +9783,7 @@
       </c>
       <c r="F466" s="3"/>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" s="3" t="s">
         <v>16</v>
       </c>
@@ -9797,7 +9801,7 @@
       </c>
       <c r="F467" s="3"/>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" s="3" t="s">
         <v>12</v>
       </c>
@@ -9833,7 +9837,7 @@
       </c>
       <c r="F469" s="3"/>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" s="3" t="s">
         <v>16</v>
       </c>
@@ -9851,7 +9855,7 @@
       </c>
       <c r="F470" s="3"/>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" s="3" t="s">
         <v>12</v>
       </c>
@@ -9887,7 +9891,7 @@
       </c>
       <c r="F472" s="3"/>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" s="3" t="s">
         <v>16</v>
       </c>
@@ -9905,7 +9909,7 @@
       </c>
       <c r="F473" s="3"/>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" s="3" t="s">
         <v>12</v>
       </c>
@@ -9941,7 +9945,7 @@
       </c>
       <c r="F475" s="3"/>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" s="3" t="s">
         <v>16</v>
       </c>
@@ -9959,7 +9963,7 @@
       </c>
       <c r="F476" s="3"/>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" s="3" t="s">
         <v>12</v>
       </c>
@@ -9995,7 +9999,7 @@
       </c>
       <c r="F478" s="3"/>
     </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" s="3" t="s">
         <v>16</v>
       </c>
@@ -10013,7 +10017,7 @@
       </c>
       <c r="F479" s="3"/>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" s="3" t="s">
         <v>12</v>
       </c>
@@ -10049,7 +10053,7 @@
       </c>
       <c r="F481" s="3"/>
     </row>
-    <row r="482" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" s="3" t="s">
         <v>16</v>
       </c>
@@ -10067,7 +10071,7 @@
       </c>
       <c r="F482" s="3"/>
     </row>
-    <row r="483" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" s="3" t="s">
         <v>12</v>
       </c>
@@ -10103,7 +10107,7 @@
       </c>
       <c r="F484" s="3"/>
     </row>
-    <row r="485" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" s="3" t="s">
         <v>16</v>
       </c>
@@ -10121,7 +10125,7 @@
       </c>
       <c r="F485" s="3"/>
     </row>
-    <row r="486" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" s="3" t="s">
         <v>12</v>
       </c>
@@ -10157,7 +10161,7 @@
       </c>
       <c r="F487" s="3"/>
     </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" s="3" t="s">
         <v>16</v>
       </c>
@@ -10175,7 +10179,7 @@
       </c>
       <c r="F488" s="3"/>
     </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" s="3" t="s">
         <v>12</v>
       </c>
@@ -10211,7 +10215,7 @@
       </c>
       <c r="F490" s="3"/>
     </row>
-    <row r="491" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" s="3" t="s">
         <v>16</v>
       </c>
@@ -10229,7 +10233,7 @@
       </c>
       <c r="F491" s="3"/>
     </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" s="3" t="s">
         <v>12</v>
       </c>
@@ -10265,7 +10269,7 @@
       </c>
       <c r="F493" s="3"/>
     </row>
-    <row r="494" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" s="3" t="s">
         <v>16</v>
       </c>
@@ -10283,7 +10287,7 @@
       </c>
       <c r="F494" s="3"/>
     </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" s="3" t="s">
         <v>12</v>
       </c>
@@ -10319,7 +10323,7 @@
       </c>
       <c r="F496" s="3"/>
     </row>
-    <row r="497" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" s="3" t="s">
         <v>16</v>
       </c>
@@ -10337,7 +10341,7 @@
       </c>
       <c r="F497" s="3"/>
     </row>
-    <row r="498" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" s="3" t="s">
         <v>12</v>
       </c>
@@ -10373,7 +10377,7 @@
       </c>
       <c r="F499" s="3"/>
     </row>
-    <row r="500" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" s="3" t="s">
         <v>16</v>
       </c>
@@ -10391,7 +10395,7 @@
       </c>
       <c r="F500" s="3"/>
     </row>
-    <row r="501" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" s="3" t="s">
         <v>12</v>
       </c>
@@ -10427,7 +10431,7 @@
       </c>
       <c r="F502" s="3"/>
     </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" s="3" t="s">
         <v>16</v>
       </c>
@@ -10445,7 +10449,7 @@
       </c>
       <c r="F503" s="3"/>
     </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" s="3" t="s">
         <v>12</v>
       </c>
@@ -10481,7 +10485,7 @@
       </c>
       <c r="F505" s="3"/>
     </row>
-    <row r="506" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" s="3" t="s">
         <v>16</v>
       </c>
@@ -10499,7 +10503,7 @@
       </c>
       <c r="F506" s="3"/>
     </row>
-    <row r="507" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" s="3" t="s">
         <v>12</v>
       </c>
@@ -10535,7 +10539,7 @@
       </c>
       <c r="F508" s="3"/>
     </row>
-    <row r="509" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" s="3" t="s">
         <v>16</v>
       </c>
@@ -10553,7 +10557,7 @@
       </c>
       <c r="F509" s="3"/>
     </row>
-    <row r="510" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" s="3" t="s">
         <v>12</v>
       </c>
@@ -10589,7 +10593,7 @@
       </c>
       <c r="F511" s="3"/>
     </row>
-    <row r="512" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" s="3" t="s">
         <v>16</v>
       </c>
@@ -10607,7 +10611,7 @@
       </c>
       <c r="F512" s="3"/>
     </row>
-    <row r="513" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" s="3" t="s">
         <v>12</v>
       </c>
@@ -10643,7 +10647,7 @@
       </c>
       <c r="F514" s="3"/>
     </row>
-    <row r="515" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" s="3" t="s">
         <v>16</v>
       </c>
@@ -10661,7 +10665,7 @@
       </c>
       <c r="F515" s="3"/>
     </row>
-    <row r="516" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" s="3" t="s">
         <v>12</v>
       </c>
@@ -10697,7 +10701,7 @@
       </c>
       <c r="F517" s="3"/>
     </row>
-    <row r="518" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" s="3" t="s">
         <v>16</v>
       </c>
@@ -10715,7 +10719,7 @@
       </c>
       <c r="F518" s="3"/>
     </row>
-    <row r="519" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" s="3" t="s">
         <v>12</v>
       </c>
@@ -10751,7 +10755,7 @@
       </c>
       <c r="F520" s="3"/>
     </row>
-    <row r="521" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" s="3" t="s">
         <v>16</v>
       </c>
@@ -10769,7 +10773,7 @@
       </c>
       <c r="F521" s="3"/>
     </row>
-    <row r="522" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" s="3" t="s">
         <v>12</v>
       </c>
@@ -10805,7 +10809,7 @@
       </c>
       <c r="F523" s="3"/>
     </row>
-    <row r="524" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" s="3" t="s">
         <v>16</v>
       </c>
@@ -10823,7 +10827,7 @@
       </c>
       <c r="F524" s="3"/>
     </row>
-    <row r="525" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" s="3" t="s">
         <v>12</v>
       </c>
@@ -10859,7 +10863,7 @@
       </c>
       <c r="F526" s="3"/>
     </row>
-    <row r="527" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" s="3" t="s">
         <v>16</v>
       </c>
@@ -10877,7 +10881,7 @@
       </c>
       <c r="F527" s="3"/>
     </row>
-    <row r="528" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" s="3" t="s">
         <v>12</v>
       </c>
@@ -10913,7 +10917,7 @@
       </c>
       <c r="F529" s="3"/>
     </row>
-    <row r="530" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" s="3" t="s">
         <v>16</v>
       </c>
@@ -10931,7 +10935,7 @@
       </c>
       <c r="F530" s="3"/>
     </row>
-    <row r="531" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" s="3" t="s">
         <v>12</v>
       </c>
@@ -10967,7 +10971,7 @@
       </c>
       <c r="F532" s="3"/>
     </row>
-    <row r="533" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" s="3" t="s">
         <v>16</v>
       </c>
@@ -10985,7 +10989,7 @@
       </c>
       <c r="F533" s="3"/>
     </row>
-    <row r="534" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" s="3" t="s">
         <v>12</v>
       </c>
@@ -11021,7 +11025,7 @@
       </c>
       <c r="F535" s="3"/>
     </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" s="3" t="s">
         <v>16</v>
       </c>
@@ -11039,7 +11043,7 @@
       </c>
       <c r="F536" s="3"/>
     </row>
-    <row r="537" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" s="3" t="s">
         <v>12</v>
       </c>
@@ -11075,7 +11079,7 @@
       </c>
       <c r="F538" s="3"/>
     </row>
-    <row r="539" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" s="3" t="s">
         <v>16</v>
       </c>
@@ -11093,7 +11097,7 @@
       </c>
       <c r="F539" s="3"/>
     </row>
-    <row r="540" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" s="3" t="s">
         <v>12</v>
       </c>
@@ -11129,7 +11133,7 @@
       </c>
       <c r="F541" s="3"/>
     </row>
-    <row r="542" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" s="3" t="s">
         <v>16</v>
       </c>
@@ -11147,7 +11151,7 @@
       </c>
       <c r="F542" s="3"/>
     </row>
-    <row r="543" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" s="3" t="s">
         <v>12</v>
       </c>
@@ -11183,7 +11187,7 @@
       </c>
       <c r="F544" s="3"/>
     </row>
-    <row r="545" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545" s="3" t="s">
         <v>16</v>
       </c>
@@ -11201,7 +11205,7 @@
       </c>
       <c r="F545" s="3"/>
     </row>
-    <row r="546" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" s="3" t="s">
         <v>12</v>
       </c>
@@ -11237,7 +11241,7 @@
       </c>
       <c r="F547" s="3"/>
     </row>
-    <row r="548" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" s="3" t="s">
         <v>16</v>
       </c>
@@ -11255,7 +11259,7 @@
       </c>
       <c r="F548" s="3"/>
     </row>
-    <row r="549" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" s="3" t="s">
         <v>12</v>
       </c>
@@ -11291,7 +11295,7 @@
       </c>
       <c r="F550" s="3"/>
     </row>
-    <row r="551" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" s="3" t="s">
         <v>16</v>
       </c>
@@ -11309,7 +11313,7 @@
       </c>
       <c r="F551" s="3"/>
     </row>
-    <row r="552" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" s="3" t="s">
         <v>12</v>
       </c>
@@ -11345,7 +11349,7 @@
       </c>
       <c r="F553" s="3"/>
     </row>
-    <row r="554" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" s="3" t="s">
         <v>16</v>
       </c>
@@ -11363,7 +11367,7 @@
       </c>
       <c r="F554" s="3"/>
     </row>
-    <row r="555" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" s="3" t="s">
         <v>12</v>
       </c>
@@ -11399,7 +11403,7 @@
       </c>
       <c r="F556" s="3"/>
     </row>
-    <row r="557" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" s="3" t="s">
         <v>16</v>
       </c>
@@ -11417,7 +11421,7 @@
       </c>
       <c r="F557" s="3"/>
     </row>
-    <row r="558" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" s="3" t="s">
         <v>12</v>
       </c>
@@ -11453,7 +11457,7 @@
       </c>
       <c r="F559" s="3"/>
     </row>
-    <row r="560" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" s="3" t="s">
         <v>16</v>
       </c>
@@ -11471,7 +11475,7 @@
       </c>
       <c r="F560" s="3"/>
     </row>
-    <row r="561" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" s="3" t="s">
         <v>12</v>
       </c>
@@ -11507,7 +11511,7 @@
       </c>
       <c r="F562" s="3"/>
     </row>
-    <row r="563" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" s="3" t="s">
         <v>16</v>
       </c>
@@ -11525,7 +11529,7 @@
       </c>
       <c r="F563" s="3"/>
     </row>
-    <row r="564" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" s="3" t="s">
         <v>12</v>
       </c>
@@ -11561,7 +11565,7 @@
       </c>
       <c r="F565" s="3"/>
     </row>
-    <row r="566" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" s="3" t="s">
         <v>16</v>
       </c>
@@ -11579,7 +11583,7 @@
       </c>
       <c r="F566" s="3"/>
     </row>
-    <row r="567" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" s="3" t="s">
         <v>12</v>
       </c>
@@ -11615,7 +11619,7 @@
       </c>
       <c r="F568" s="3"/>
     </row>
-    <row r="569" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" s="3" t="s">
         <v>16</v>
       </c>
@@ -11633,7 +11637,7 @@
       </c>
       <c r="F569" s="3"/>
     </row>
-    <row r="570" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" s="3" t="s">
         <v>12</v>
       </c>
@@ -11669,7 +11673,7 @@
       </c>
       <c r="F571" s="3"/>
     </row>
-    <row r="572" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" s="3" t="s">
         <v>16</v>
       </c>
@@ -11687,7 +11691,7 @@
       </c>
       <c r="F572" s="3"/>
     </row>
-    <row r="573" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" s="3" t="s">
         <v>12</v>
       </c>
@@ -11723,7 +11727,7 @@
       </c>
       <c r="F574" s="3"/>
     </row>
-    <row r="575" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" s="3" t="s">
         <v>16</v>
       </c>
@@ -11741,7 +11745,7 @@
       </c>
       <c r="F575" s="3"/>
     </row>
-    <row r="576" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576" s="3" t="s">
         <v>12</v>
       </c>
@@ -11777,7 +11781,7 @@
       </c>
       <c r="F577" s="3"/>
     </row>
-    <row r="578" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578" s="3" t="s">
         <v>16</v>
       </c>
@@ -11795,7 +11799,7 @@
       </c>
       <c r="F578" s="3"/>
     </row>
-    <row r="579" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579" s="3" t="s">
         <v>12</v>
       </c>
@@ -11831,7 +11835,7 @@
       </c>
       <c r="F580" s="3"/>
     </row>
-    <row r="581" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581" s="3" t="s">
         <v>16</v>
       </c>
@@ -11849,7 +11853,7 @@
       </c>
       <c r="F581" s="3"/>
     </row>
-    <row r="582" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582" s="3" t="s">
         <v>12</v>
       </c>
@@ -11885,7 +11889,7 @@
       </c>
       <c r="F583" s="3"/>
     </row>
-    <row r="584" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" s="3" t="s">
         <v>16</v>
       </c>
@@ -11903,7 +11907,7 @@
       </c>
       <c r="F584" s="3"/>
     </row>
-    <row r="585" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" s="3" t="s">
         <v>12</v>
       </c>
@@ -11939,7 +11943,7 @@
       </c>
       <c r="F586" s="3"/>
     </row>
-    <row r="587" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" s="3" t="s">
         <v>16</v>
       </c>
@@ -11957,7 +11961,7 @@
       </c>
       <c r="F587" s="3"/>
     </row>
-    <row r="588" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" s="3" t="s">
         <v>12</v>
       </c>
@@ -11993,7 +11997,7 @@
       </c>
       <c r="F589" s="3"/>
     </row>
-    <row r="590" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" s="3" t="s">
         <v>16</v>
       </c>
@@ -12011,7 +12015,7 @@
       </c>
       <c r="F590" s="3"/>
     </row>
-    <row r="591" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" s="3" t="s">
         <v>12</v>
       </c>
@@ -12047,7 +12051,7 @@
       </c>
       <c r="F592" s="3"/>
     </row>
-    <row r="593" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593" s="3" t="s">
         <v>16</v>
       </c>
@@ -12065,7 +12069,7 @@
       </c>
       <c r="F593" s="3"/>
     </row>
-    <row r="594" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594" s="3" t="s">
         <v>12</v>
       </c>
@@ -12101,7 +12105,7 @@
       </c>
       <c r="F595" s="3"/>
     </row>
-    <row r="596" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596" s="3" t="s">
         <v>16</v>
       </c>
@@ -12119,7 +12123,7 @@
       </c>
       <c r="F596" s="3"/>
     </row>
-    <row r="597" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" s="3" t="s">
         <v>12</v>
       </c>
@@ -12155,7 +12159,7 @@
       </c>
       <c r="F598" s="3"/>
     </row>
-    <row r="599" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599" s="3" t="s">
         <v>16</v>
       </c>
@@ -12173,7 +12177,7 @@
       </c>
       <c r="F599" s="3"/>
     </row>
-    <row r="600" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600" s="3" t="s">
         <v>12</v>
       </c>
@@ -12209,7 +12213,7 @@
       </c>
       <c r="F601" s="3"/>
     </row>
-    <row r="602" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" s="3" t="s">
         <v>16</v>
       </c>
@@ -12227,7 +12231,7 @@
       </c>
       <c r="F602" s="3"/>
     </row>
-    <row r="603" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603" s="3" t="s">
         <v>12</v>
       </c>
@@ -12263,7 +12267,7 @@
       </c>
       <c r="F604" s="3"/>
     </row>
-    <row r="605" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" s="3" t="s">
         <v>16</v>
       </c>
@@ -12281,7 +12285,7 @@
       </c>
       <c r="F605" s="3"/>
     </row>
-    <row r="606" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606" s="3" t="s">
         <v>12</v>
       </c>
@@ -12317,7 +12321,7 @@
       </c>
       <c r="F607" s="3"/>
     </row>
-    <row r="608" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A608" s="3" t="s">
         <v>16</v>
       </c>
@@ -12335,7 +12339,7 @@
       </c>
       <c r="F608" s="3"/>
     </row>
-    <row r="609" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" s="3" t="s">
         <v>12</v>
       </c>
@@ -12371,7 +12375,7 @@
       </c>
       <c r="F610" s="3"/>
     </row>
-    <row r="611" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611" s="3" t="s">
         <v>16</v>
       </c>
@@ -12389,7 +12393,7 @@
       </c>
       <c r="F611" s="3"/>
     </row>
-    <row r="612" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612" s="3" t="s">
         <v>12</v>
       </c>
@@ -12425,7 +12429,7 @@
       </c>
       <c r="F613" s="3"/>
     </row>
-    <row r="614" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614" s="3" t="s">
         <v>16</v>
       </c>
@@ -12443,7 +12447,7 @@
       </c>
       <c r="F614" s="3"/>
     </row>
-    <row r="615" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" s="3" t="s">
         <v>12</v>
       </c>
@@ -12479,7 +12483,7 @@
       </c>
       <c r="F616" s="3"/>
     </row>
-    <row r="617" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617" s="3" t="s">
         <v>16</v>
       </c>
@@ -12497,7 +12501,7 @@
       </c>
       <c r="F617" s="3"/>
     </row>
-    <row r="618" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" s="3" t="s">
         <v>12</v>
       </c>
@@ -12533,7 +12537,7 @@
       </c>
       <c r="F619" s="3"/>
     </row>
-    <row r="620" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" s="3" t="s">
         <v>16</v>
       </c>
@@ -12551,7 +12555,7 @@
       </c>
       <c r="F620" s="3"/>
     </row>
-    <row r="621" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" s="3" t="s">
         <v>12</v>
       </c>
@@ -12587,7 +12591,7 @@
       </c>
       <c r="F622" s="3"/>
     </row>
-    <row r="623" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" s="3" t="s">
         <v>16</v>
       </c>
@@ -12605,7 +12609,7 @@
       </c>
       <c r="F623" s="3"/>
     </row>
-    <row r="624" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624" s="3" t="s">
         <v>12</v>
       </c>
@@ -12641,7 +12645,7 @@
       </c>
       <c r="F625" s="3"/>
     </row>
-    <row r="626" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A626" s="3" t="s">
         <v>16</v>
       </c>
@@ -12659,7 +12663,7 @@
       </c>
       <c r="F626" s="3"/>
     </row>
-    <row r="627" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" s="3" t="s">
         <v>12</v>
       </c>
@@ -12695,7 +12699,7 @@
       </c>
       <c r="F628" s="3"/>
     </row>
-    <row r="629" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629" s="3" t="s">
         <v>16</v>
       </c>
@@ -12713,7 +12717,7 @@
       </c>
       <c r="F629" s="3"/>
     </row>
-    <row r="630" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A630" s="3" t="s">
         <v>12</v>
       </c>
@@ -12749,7 +12753,7 @@
       </c>
       <c r="F631" s="3"/>
     </row>
-    <row r="632" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632" s="3" t="s">
         <v>16</v>
       </c>
@@ -12767,7 +12771,7 @@
       </c>
       <c r="F632" s="3"/>
     </row>
-    <row r="633" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633" s="3" t="s">
         <v>12</v>
       </c>
@@ -12803,7 +12807,7 @@
       </c>
       <c r="F634" s="3"/>
     </row>
-    <row r="635" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635" s="3" t="s">
         <v>16</v>
       </c>
@@ -12821,7 +12825,7 @@
       </c>
       <c r="F635" s="3"/>
     </row>
-    <row r="636" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A636" s="3" t="s">
         <v>12</v>
       </c>
@@ -12857,7 +12861,7 @@
       </c>
       <c r="F637" s="3"/>
     </row>
-    <row r="638" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638" s="3" t="s">
         <v>16</v>
       </c>
@@ -12875,7 +12879,7 @@
       </c>
       <c r="F638" s="3"/>
     </row>
-    <row r="639" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639" s="3" t="s">
         <v>12</v>
       </c>
@@ -12911,7 +12915,7 @@
       </c>
       <c r="F640" s="3"/>
     </row>
-    <row r="641" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641" s="3" t="s">
         <v>16</v>
       </c>
@@ -12929,7 +12933,7 @@
       </c>
       <c r="F641" s="3"/>
     </row>
-    <row r="642" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642" s="3" t="s">
         <v>12</v>
       </c>
@@ -12965,7 +12969,7 @@
       </c>
       <c r="F643" s="3"/>
     </row>
-    <row r="644" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644" s="3" t="s">
         <v>16</v>
       </c>
@@ -12983,7 +12987,7 @@
       </c>
       <c r="F644" s="3"/>
     </row>
-    <row r="645" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645" s="3" t="s">
         <v>12</v>
       </c>
@@ -13019,7 +13023,7 @@
       </c>
       <c r="F646" s="3"/>
     </row>
-    <row r="647" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647" s="3" t="s">
         <v>16</v>
       </c>
@@ -13037,7 +13041,7 @@
       </c>
       <c r="F647" s="3"/>
     </row>
-    <row r="648" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A648" s="3" t="s">
         <v>12</v>
       </c>
@@ -13073,7 +13077,7 @@
       </c>
       <c r="F649" s="3"/>
     </row>
-    <row r="650" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A650" s="3" t="s">
         <v>16</v>
       </c>
@@ -13091,7 +13095,7 @@
       </c>
       <c r="F650" s="3"/>
     </row>
-    <row r="651" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651" s="3" t="s">
         <v>12</v>
       </c>
@@ -13127,7 +13131,7 @@
       </c>
       <c r="F652" s="3"/>
     </row>
-    <row r="653" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653" s="3" t="s">
         <v>16</v>
       </c>
@@ -13145,7 +13149,7 @@
       </c>
       <c r="F653" s="3"/>
     </row>
-    <row r="654" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A654" s="3" t="s">
         <v>12</v>
       </c>
@@ -13181,7 +13185,7 @@
       </c>
       <c r="F655" s="3"/>
     </row>
-    <row r="656" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656" s="3" t="s">
         <v>16</v>
       </c>
@@ -13199,7 +13203,7 @@
       </c>
       <c r="F656" s="3"/>
     </row>
-    <row r="657" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657" s="3" t="s">
         <v>12</v>
       </c>
@@ -13235,7 +13239,7 @@
       </c>
       <c r="F658" s="3"/>
     </row>
-    <row r="659" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659" s="3" t="s">
         <v>16</v>
       </c>
@@ -13253,7 +13257,7 @@
       </c>
       <c r="F659" s="3"/>
     </row>
-    <row r="660" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A660" s="3" t="s">
         <v>12</v>
       </c>
@@ -13289,7 +13293,7 @@
       </c>
       <c r="F661" s="3"/>
     </row>
-    <row r="662" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A662" s="3" t="s">
         <v>16</v>
       </c>
@@ -13307,7 +13311,7 @@
       </c>
       <c r="F662" s="3"/>
     </row>
-    <row r="663" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663" s="3" t="s">
         <v>12</v>
       </c>
@@ -13343,7 +13347,7 @@
       </c>
       <c r="F664" s="3"/>
     </row>
-    <row r="665" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665" s="3" t="s">
         <v>16</v>
       </c>
@@ -13361,7 +13365,7 @@
       </c>
       <c r="F665" s="3"/>
     </row>
-    <row r="666" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A666" s="3" t="s">
         <v>12</v>
       </c>
@@ -13397,7 +13401,7 @@
       </c>
       <c r="F667" s="3"/>
     </row>
-    <row r="668" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A668" s="3" t="s">
         <v>16</v>
       </c>
@@ -13415,7 +13419,7 @@
       </c>
       <c r="F668" s="3"/>
     </row>
-    <row r="669" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A669" s="3" t="s">
         <v>12</v>
       </c>
@@ -13451,7 +13455,7 @@
       </c>
       <c r="F670" s="3"/>
     </row>
-    <row r="671" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A671" s="3" t="s">
         <v>16</v>
       </c>
@@ -13469,7 +13473,7 @@
       </c>
       <c r="F671" s="3"/>
     </row>
-    <row r="672" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A672" s="3" t="s">
         <v>12</v>
       </c>
@@ -13505,7 +13509,7 @@
       </c>
       <c r="F673" s="3"/>
     </row>
-    <row r="674" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A674" s="3" t="s">
         <v>16</v>
       </c>
@@ -13523,7 +13527,7 @@
       </c>
       <c r="F674" s="3"/>
     </row>
-    <row r="675" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A675" s="3" t="s">
         <v>12</v>
       </c>
@@ -13559,7 +13563,7 @@
       </c>
       <c r="F676" s="3"/>
     </row>
-    <row r="677" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A677" s="3" t="s">
         <v>16</v>
       </c>
@@ -13577,7 +13581,7 @@
       </c>
       <c r="F677" s="3"/>
     </row>
-    <row r="678" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A678" s="3" t="s">
         <v>12</v>
       </c>
@@ -13613,7 +13617,7 @@
       </c>
       <c r="F679" s="3"/>
     </row>
-    <row r="680" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A680" s="3" t="s">
         <v>16</v>
       </c>
@@ -13631,7 +13635,7 @@
       </c>
       <c r="F680" s="3"/>
     </row>
-    <row r="681" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A681" s="3" t="s">
         <v>12</v>
       </c>
@@ -13667,7 +13671,7 @@
       </c>
       <c r="F682" s="3"/>
     </row>
-    <row r="683" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683" s="3" t="s">
         <v>16</v>
       </c>
@@ -13685,7 +13689,7 @@
       </c>
       <c r="F683" s="3"/>
     </row>
-    <row r="684" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A684" s="3" t="s">
         <v>12</v>
       </c>
@@ -13721,7 +13725,7 @@
       </c>
       <c r="F685" s="3"/>
     </row>
-    <row r="686" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A686" s="3" t="s">
         <v>16</v>
       </c>
@@ -13739,7 +13743,7 @@
       </c>
       <c r="F686" s="3"/>
     </row>
-    <row r="687" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687" s="3" t="s">
         <v>12</v>
       </c>
@@ -13775,7 +13779,7 @@
       </c>
       <c r="F688" s="3"/>
     </row>
-    <row r="689" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689" s="3" t="s">
         <v>16</v>
       </c>
@@ -13793,7 +13797,7 @@
       </c>
       <c r="F689" s="3"/>
     </row>
-    <row r="690" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690" s="3" t="s">
         <v>12</v>
       </c>
@@ -13829,7 +13833,7 @@
       </c>
       <c r="F691" s="3"/>
     </row>
-    <row r="692" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A692" s="3" t="s">
         <v>16</v>
       </c>
@@ -13847,7 +13851,7 @@
       </c>
       <c r="F692" s="3"/>
     </row>
-    <row r="693" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693" s="3" t="s">
         <v>12</v>
       </c>
@@ -13883,7 +13887,7 @@
       </c>
       <c r="F694" s="3"/>
     </row>
-    <row r="695" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" s="3" t="s">
         <v>16</v>
       </c>
@@ -13901,7 +13905,7 @@
       </c>
       <c r="F695" s="3"/>
     </row>
-    <row r="696" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A696" s="3" t="s">
         <v>12</v>
       </c>
@@ -13937,7 +13941,7 @@
       </c>
       <c r="F697" s="3"/>
     </row>
-    <row r="698" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698" s="3" t="s">
         <v>16</v>
       </c>
@@ -13955,7 +13959,7 @@
       </c>
       <c r="F698" s="3"/>
     </row>
-    <row r="699" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699" s="3" t="s">
         <v>12</v>
       </c>
@@ -13991,7 +13995,7 @@
       </c>
       <c r="F700" s="3"/>
     </row>
-    <row r="701" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701" s="3" t="s">
         <v>16</v>
       </c>
@@ -14009,7 +14013,7 @@
       </c>
       <c r="F701" s="3"/>
     </row>
-    <row r="702" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702" s="3" t="s">
         <v>12</v>
       </c>
@@ -14045,7 +14049,7 @@
       </c>
       <c r="F703" s="3"/>
     </row>
-    <row r="704" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A704" s="3" t="s">
         <v>16</v>
       </c>
@@ -14063,7 +14067,7 @@
       </c>
       <c r="F704" s="3"/>
     </row>
-    <row r="705" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A705" s="3" t="s">
         <v>12</v>
       </c>
@@ -14099,7 +14103,7 @@
       </c>
       <c r="F706" s="3"/>
     </row>
-    <row r="707" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707" s="3" t="s">
         <v>16</v>
       </c>
@@ -14117,7 +14121,7 @@
       </c>
       <c r="F707" s="3"/>
     </row>
-    <row r="708" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A708" s="3" t="s">
         <v>12</v>
       </c>
@@ -14153,7 +14157,7 @@
       </c>
       <c r="F709" s="3"/>
     </row>
-    <row r="710" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A710" s="3" t="s">
         <v>16</v>
       </c>
@@ -14171,7 +14175,7 @@
       </c>
       <c r="F710" s="3"/>
     </row>
-    <row r="711" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A711" s="3" t="s">
         <v>12</v>
       </c>
@@ -14207,7 +14211,7 @@
       </c>
       <c r="F712" s="3"/>
     </row>
-    <row r="713" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A713" s="3" t="s">
         <v>16</v>
       </c>
@@ -14225,7 +14229,7 @@
       </c>
       <c r="F713" s="3"/>
     </row>
-    <row r="714" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A714" s="3" t="s">
         <v>12</v>
       </c>
@@ -14261,7 +14265,7 @@
       </c>
       <c r="F715" s="3"/>
     </row>
-    <row r="716" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A716" s="3" t="s">
         <v>16</v>
       </c>
@@ -14279,7 +14283,7 @@
       </c>
       <c r="F716" s="3"/>
     </row>
-    <row r="717" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A717" s="3" t="s">
         <v>12</v>
       </c>
@@ -14315,7 +14319,7 @@
       </c>
       <c r="F718" s="3"/>
     </row>
-    <row r="719" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719" s="3" t="s">
         <v>16</v>
       </c>
@@ -14333,7 +14337,7 @@
       </c>
       <c r="F719" s="3"/>
     </row>
-    <row r="720" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A720" s="3" t="s">
         <v>12</v>
       </c>
@@ -14369,7 +14373,7 @@
       </c>
       <c r="F721" s="3"/>
     </row>
-    <row r="722" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A722" s="3" t="s">
         <v>16</v>
       </c>
@@ -14387,7 +14391,7 @@
       </c>
       <c r="F722" s="3"/>
     </row>
-    <row r="723" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A723" s="3" t="s">
         <v>12</v>
       </c>
@@ -14423,7 +14427,7 @@
       </c>
       <c r="F724" s="3"/>
     </row>
-    <row r="725" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A725" s="3" t="s">
         <v>16</v>
       </c>
@@ -14441,7 +14445,7 @@
       </c>
       <c r="F725" s="3"/>
     </row>
-    <row r="726" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A726" s="3" t="s">
         <v>12</v>
       </c>
@@ -14477,7 +14481,7 @@
       </c>
       <c r="F727" s="3"/>
     </row>
-    <row r="728" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A728" s="3" t="s">
         <v>16</v>
       </c>
@@ -14495,7 +14499,7 @@
       </c>
       <c r="F728" s="3"/>
     </row>
-    <row r="729" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A729" s="3" t="s">
         <v>12</v>
       </c>
@@ -14531,7 +14535,7 @@
       </c>
       <c r="F730" s="3"/>
     </row>
-    <row r="731" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A731" s="3" t="s">
         <v>16</v>
       </c>
@@ -14549,7 +14553,7 @@
       </c>
       <c r="F731" s="3"/>
     </row>
-    <row r="732" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A732" s="3" t="s">
         <v>12</v>
       </c>
@@ -14585,7 +14589,7 @@
       </c>
       <c r="F733" s="3"/>
     </row>
-    <row r="734" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A734" s="3" t="s">
         <v>16</v>
       </c>
@@ -14603,7 +14607,7 @@
       </c>
       <c r="F734" s="3"/>
     </row>
-    <row r="735" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A735" s="3" t="s">
         <v>12</v>
       </c>
@@ -14639,7 +14643,7 @@
       </c>
       <c r="F736" s="3"/>
     </row>
-    <row r="737" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A737" s="3" t="s">
         <v>16</v>
       </c>
@@ -14657,7 +14661,7 @@
       </c>
       <c r="F737" s="3"/>
     </row>
-    <row r="738" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A738" s="3" t="s">
         <v>12</v>
       </c>
@@ -14693,7 +14697,7 @@
       </c>
       <c r="F739" s="3"/>
     </row>
-    <row r="740" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A740" s="3" t="s">
         <v>16</v>
       </c>
@@ -14711,7 +14715,7 @@
       </c>
       <c r="F740" s="3"/>
     </row>
-    <row r="741" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A741" s="3" t="s">
         <v>12</v>
       </c>
@@ -14747,7 +14751,7 @@
       </c>
       <c r="F742" s="3"/>
     </row>
-    <row r="743" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A743" s="3" t="s">
         <v>16</v>
       </c>
@@ -14765,7 +14769,7 @@
       </c>
       <c r="F743" s="3"/>
     </row>
-    <row r="744" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A744" s="3" t="s">
         <v>12</v>
       </c>
@@ -14801,7 +14805,7 @@
       </c>
       <c r="F745" s="3"/>
     </row>
-    <row r="746" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A746" s="3" t="s">
         <v>16</v>
       </c>
@@ -14819,7 +14823,7 @@
       </c>
       <c r="F746" s="3"/>
     </row>
-    <row r="747" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A747" s="3" t="s">
         <v>12</v>
       </c>
@@ -14855,7 +14859,7 @@
       </c>
       <c r="F748" s="3"/>
     </row>
-    <row r="749" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A749" s="3" t="s">
         <v>16</v>
       </c>
@@ -14873,7 +14877,7 @@
       </c>
       <c r="F749" s="3"/>
     </row>
-    <row r="750" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A750" s="3" t="s">
         <v>12</v>
       </c>
@@ -14909,7 +14913,7 @@
       </c>
       <c r="F751" s="3"/>
     </row>
-    <row r="752" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A752" s="3" t="s">
         <v>16</v>
       </c>
@@ -14927,7 +14931,7 @@
       </c>
       <c r="F752" s="3"/>
     </row>
-    <row r="753" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A753" s="3" t="s">
         <v>12</v>
       </c>
@@ -14963,7 +14967,7 @@
       </c>
       <c r="F754" s="3"/>
     </row>
-    <row r="755" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A755" s="3" t="s">
         <v>16</v>
       </c>
@@ -14981,7 +14985,7 @@
       </c>
       <c r="F755" s="3"/>
     </row>
-    <row r="756" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A756" s="3" t="s">
         <v>12</v>
       </c>
@@ -15017,7 +15021,7 @@
       </c>
       <c r="F757" s="3"/>
     </row>
-    <row r="758" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A758" s="3" t="s">
         <v>16</v>
       </c>
@@ -15035,7 +15039,7 @@
       </c>
       <c r="F758" s="3"/>
     </row>
-    <row r="759" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A759" s="3" t="s">
         <v>12</v>
       </c>
@@ -15071,7 +15075,7 @@
       </c>
       <c r="F760" s="3"/>
     </row>
-    <row r="761" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A761" s="3" t="s">
         <v>16</v>
       </c>
@@ -15089,7 +15093,7 @@
       </c>
       <c r="F761" s="3"/>
     </row>
-    <row r="762" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A762" s="3" t="s">
         <v>12</v>
       </c>
@@ -15125,7 +15129,7 @@
       </c>
       <c r="F763" s="3"/>
     </row>
-    <row r="764" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A764" s="3" t="s">
         <v>16</v>
       </c>
@@ -15143,7 +15147,7 @@
       </c>
       <c r="F764" s="3"/>
     </row>
-    <row r="765" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A765" s="3" t="s">
         <v>12</v>
       </c>
@@ -15179,7 +15183,7 @@
       </c>
       <c r="F766" s="3"/>
     </row>
-    <row r="767" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A767" s="3" t="s">
         <v>16</v>
       </c>
@@ -15197,7 +15201,7 @@
       </c>
       <c r="F767" s="3"/>
     </row>
-    <row r="768" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A768" s="3" t="s">
         <v>12</v>
       </c>
@@ -15233,7 +15237,7 @@
       </c>
       <c r="F769" s="3"/>
     </row>
-    <row r="770" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A770" s="3" t="s">
         <v>16</v>
       </c>
@@ -15251,7 +15255,7 @@
       </c>
       <c r="F770" s="3"/>
     </row>
-    <row r="771" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A771" s="3" t="s">
         <v>12</v>
       </c>
@@ -15287,7 +15291,7 @@
       </c>
       <c r="F772" s="3"/>
     </row>
-    <row r="773" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A773" s="3" t="s">
         <v>16</v>
       </c>
@@ -15305,7 +15309,7 @@
       </c>
       <c r="F773" s="3"/>
     </row>
-    <row r="774" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A774" s="3" t="s">
         <v>12</v>
       </c>
@@ -15341,7 +15345,7 @@
       </c>
       <c r="F775" s="3"/>
     </row>
-    <row r="776" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A776" s="3" t="s">
         <v>16</v>
       </c>
@@ -15359,7 +15363,7 @@
       </c>
       <c r="F776" s="3"/>
     </row>
-    <row r="777" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A777" s="3" t="s">
         <v>12</v>
       </c>
@@ -15395,7 +15399,7 @@
       </c>
       <c r="F778" s="3"/>
     </row>
-    <row r="779" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A779" s="3" t="s">
         <v>16</v>
       </c>
@@ -15413,7 +15417,7 @@
       </c>
       <c r="F779" s="3"/>
     </row>
-    <row r="780" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A780" s="3" t="s">
         <v>12</v>
       </c>
@@ -15449,7 +15453,7 @@
       </c>
       <c r="F781" s="3"/>
     </row>
-    <row r="782" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A782" s="3" t="s">
         <v>16</v>
       </c>
@@ -15467,7 +15471,7 @@
       </c>
       <c r="F782" s="3"/>
     </row>
-    <row r="783" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A783" s="3" t="s">
         <v>12</v>
       </c>
@@ -15503,7 +15507,7 @@
       </c>
       <c r="F784" s="3"/>
     </row>
-    <row r="785" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A785" s="3" t="s">
         <v>16</v>
       </c>
@@ -15521,7 +15525,7 @@
       </c>
       <c r="F785" s="3"/>
     </row>
-    <row r="786" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A786" s="3" t="s">
         <v>12</v>
       </c>
@@ -15557,7 +15561,7 @@
       </c>
       <c r="F787" s="3"/>
     </row>
-    <row r="788" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A788" s="3" t="s">
         <v>16</v>
       </c>
@@ -15575,7 +15579,7 @@
       </c>
       <c r="F788" s="3"/>
     </row>
-    <row r="789" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A789" s="3" t="s">
         <v>12</v>
       </c>
@@ -15611,7 +15615,7 @@
       </c>
       <c r="F790" s="3"/>
     </row>
-    <row r="791" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A791" s="3" t="s">
         <v>16</v>
       </c>
@@ -15629,7 +15633,7 @@
       </c>
       <c r="F791" s="3"/>
     </row>
-    <row r="792" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A792" s="3" t="s">
         <v>12</v>
       </c>
@@ -15665,7 +15669,7 @@
       </c>
       <c r="F793" s="3"/>
     </row>
-    <row r="794" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A794" s="3" t="s">
         <v>16</v>
       </c>
@@ -15683,7 +15687,7 @@
       </c>
       <c r="F794" s="3"/>
     </row>
-    <row r="795" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A795" s="3" t="s">
         <v>12</v>
       </c>
@@ -15719,7 +15723,7 @@
       </c>
       <c r="F796" s="3"/>
     </row>
-    <row r="797" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A797" s="3" t="s">
         <v>16</v>
       </c>
@@ -15737,7 +15741,7 @@
       </c>
       <c r="F797" s="3"/>
     </row>
-    <row r="798" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A798" s="3" t="s">
         <v>12</v>
       </c>
@@ -15773,7 +15777,7 @@
       </c>
       <c r="F799" s="3"/>
     </row>
-    <row r="800" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A800" s="3" t="s">
         <v>16</v>
       </c>
@@ -15791,7 +15795,7 @@
       </c>
       <c r="F800" s="3"/>
     </row>
-    <row r="801" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A801" s="3" t="s">
         <v>12</v>
       </c>
@@ -15827,7 +15831,7 @@
       </c>
       <c r="F802" s="3"/>
     </row>
-    <row r="803" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A803" s="3" t="s">
         <v>16</v>
       </c>
@@ -15845,7 +15849,7 @@
       </c>
       <c r="F803" s="3"/>
     </row>
-    <row r="804" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A804" s="3" t="s">
         <v>12</v>
       </c>
@@ -15881,7 +15885,7 @@
       </c>
       <c r="F805" s="3"/>
     </row>
-    <row r="806" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A806" s="3" t="s">
         <v>16</v>
       </c>
@@ -15899,7 +15903,7 @@
       </c>
       <c r="F806" s="3"/>
     </row>
-    <row r="807" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A807" s="3" t="s">
         <v>12</v>
       </c>
@@ -15935,7 +15939,7 @@
       </c>
       <c r="F808" s="3"/>
     </row>
-    <row r="809" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A809" s="3" t="s">
         <v>16</v>
       </c>
@@ -15953,7 +15957,7 @@
       </c>
       <c r="F809" s="3"/>
     </row>
-    <row r="810" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A810" s="3" t="s">
         <v>12</v>
       </c>
@@ -15989,7 +15993,7 @@
       </c>
       <c r="F811" s="3"/>
     </row>
-    <row r="812" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A812" s="3" t="s">
         <v>16</v>
       </c>
@@ -16007,7 +16011,7 @@
       </c>
       <c r="F812" s="3"/>
     </row>
-    <row r="813" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A813" s="3" t="s">
         <v>12</v>
       </c>
@@ -16043,7 +16047,7 @@
       </c>
       <c r="F814" s="3"/>
     </row>
-    <row r="815" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A815" s="3" t="s">
         <v>16</v>
       </c>
@@ -16061,7 +16065,7 @@
       </c>
       <c r="F815" s="3"/>
     </row>
-    <row r="816" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A816" s="3" t="s">
         <v>12</v>
       </c>
@@ -16097,7 +16101,7 @@
       </c>
       <c r="F817" s="3"/>
     </row>
-    <row r="818" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A818" s="3" t="s">
         <v>16</v>
       </c>
@@ -16115,7 +16119,7 @@
       </c>
       <c r="F818" s="3"/>
     </row>
-    <row r="819" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A819" s="3" t="s">
         <v>12</v>
       </c>
@@ -16151,7 +16155,7 @@
       </c>
       <c r="F820" s="3"/>
     </row>
-    <row r="821" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A821" s="3" t="s">
         <v>16</v>
       </c>
@@ -16169,7 +16173,7 @@
       </c>
       <c r="F821" s="3"/>
     </row>
-    <row r="822" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A822" s="3" t="s">
         <v>12</v>
       </c>
@@ -16205,7 +16209,7 @@
       </c>
       <c r="F823" s="3"/>
     </row>
-    <row r="824" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A824" s="3" t="s">
         <v>16</v>
       </c>
@@ -16223,7 +16227,7 @@
       </c>
       <c r="F824" s="3"/>
     </row>
-    <row r="825" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A825" s="3" t="s">
         <v>12</v>
       </c>
@@ -16259,7 +16263,7 @@
       </c>
       <c r="F826" s="3"/>
     </row>
-    <row r="827" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A827" s="3" t="s">
         <v>16</v>
       </c>
@@ -16277,7 +16281,7 @@
       </c>
       <c r="F827" s="3"/>
     </row>
-    <row r="828" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A828" s="3" t="s">
         <v>12</v>
       </c>
@@ -16313,7 +16317,7 @@
       </c>
       <c r="F829" s="3"/>
     </row>
-    <row r="830" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A830" s="3" t="s">
         <v>16</v>
       </c>
@@ -16331,7 +16335,7 @@
       </c>
       <c r="F830" s="3"/>
     </row>
-    <row r="831" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A831" s="3" t="s">
         <v>12</v>
       </c>
@@ -16367,7 +16371,7 @@
       </c>
       <c r="F832" s="3"/>
     </row>
-    <row r="833" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A833" s="3" t="s">
         <v>16</v>
       </c>
@@ -16385,7 +16389,7 @@
       </c>
       <c r="F833" s="3"/>
     </row>
-    <row r="834" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A834" s="3" t="s">
         <v>12</v>
       </c>
@@ -16421,7 +16425,7 @@
       </c>
       <c r="F835" s="3"/>
     </row>
-    <row r="836" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A836" s="3" t="s">
         <v>16</v>
       </c>
@@ -16439,7 +16443,7 @@
       </c>
       <c r="F836" s="3"/>
     </row>
-    <row r="837" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A837" s="3" t="s">
         <v>12</v>
       </c>
@@ -16475,7 +16479,7 @@
       </c>
       <c r="F838" s="3"/>
     </row>
-    <row r="839" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A839" s="3" t="s">
         <v>16</v>
       </c>
@@ -16493,7 +16497,7 @@
       </c>
       <c r="F839" s="3"/>
     </row>
-    <row r="840" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A840" s="3" t="s">
         <v>12</v>
       </c>
@@ -16529,7 +16533,7 @@
       </c>
       <c r="F841" s="3"/>
     </row>
-    <row r="842" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A842" s="3" t="s">
         <v>16</v>
       </c>
@@ -16547,7 +16551,7 @@
       </c>
       <c r="F842" s="3"/>
     </row>
-    <row r="843" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A843" s="3" t="s">
         <v>12</v>
       </c>
@@ -16583,7 +16587,7 @@
       </c>
       <c r="F844" s="3"/>
     </row>
-    <row r="845" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A845" s="3" t="s">
         <v>16</v>
       </c>
@@ -16601,7 +16605,7 @@
       </c>
       <c r="F845" s="3"/>
     </row>
-    <row r="846" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A846" s="3" t="s">
         <v>12</v>
       </c>
@@ -16637,7 +16641,7 @@
       </c>
       <c r="F847" s="3"/>
     </row>
-    <row r="848" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A848" s="3" t="s">
         <v>16</v>
       </c>
@@ -16655,7 +16659,7 @@
       </c>
       <c r="F848" s="3"/>
     </row>
-    <row r="849" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A849" s="3" t="s">
         <v>12</v>
       </c>
@@ -16691,7 +16695,7 @@
       </c>
       <c r="F850" s="3"/>
     </row>
-    <row r="851" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A851" s="3" t="s">
         <v>16</v>
       </c>
@@ -16710,6 +16714,13 @@
       <c r="F851" s="3"/>
     </row>
   </sheetData>
+  <autoFilter ref="A2:F851" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="A102"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
